--- a/java/spring/org.springframework.core.xlsx
+++ b/java/spring/org.springframework.core.xlsx
@@ -4,17 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564"/>
+    <workbookView windowWidth="21648" windowHeight="9155" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="org.springframework.core" sheetId="2" r:id="rId1"/>
+    <sheet name="org.springframework.core子包" sheetId="3" r:id="rId2"/>
+    <sheet name="spring-core其他包" sheetId="6" r:id="rId3"/>
+    <sheet name="spring-expression" sheetId="4" r:id="rId4"/>
+    <sheet name="spring-context" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="537">
   <si>
     <t>AliasRegistry</t>
   </si>
@@ -158,6 +162,1640 @@
   </si>
   <si>
     <t>StandardReflectionParameterNameDiscoverer</t>
+  </si>
+  <si>
+    <t>org.springframework.core.annotation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Interfaces</t>
+    </r>
+  </si>
+  <si>
+    <t>AnnotationFilter</t>
+  </si>
+  <si>
+    <t>MergedAnnotation</t>
+  </si>
+  <si>
+    <t>MergedAnnotations</t>
+  </si>
+  <si>
+    <t>MergedAnnotationSelector</t>
+  </si>
+  <si>
+    <t>SynthesizedAnnotation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Classes</t>
+    </r>
+  </si>
+  <si>
+    <t>AnnotatedElementUtils</t>
+  </si>
+  <si>
+    <t>AnnotationAttributes</t>
+  </si>
+  <si>
+    <t>AnnotationAwareOrderComparator</t>
+  </si>
+  <si>
+    <t>AnnotationUtils</t>
+  </si>
+  <si>
+    <t>MergedAnnotationCollectors</t>
+  </si>
+  <si>
+    <t>MergedAnnotationPredicates</t>
+  </si>
+  <si>
+    <t>MergedAnnotationSelectors</t>
+  </si>
+  <si>
+    <t>OrderUtils</t>
+  </si>
+  <si>
+    <t>RepeatableContainers</t>
+  </si>
+  <si>
+    <t>SynthesizingMethodParameter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Enums</t>
+    </r>
+  </si>
+  <si>
+    <t>MergedAnnotation.Adapt</t>
+  </si>
+  <si>
+    <t>MergedAnnotations.SearchStrategy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Exceptions</t>
+    </r>
+  </si>
+  <si>
+    <t>AnnotationConfigurationException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Annotation Types</t>
+    </r>
+  </si>
+  <si>
+    <t>AliasFor</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.codec</t>
+    </r>
+  </si>
+  <si>
+    <t>Decoder</t>
+  </si>
+  <si>
+    <t>Encoder</t>
+  </si>
+  <si>
+    <t>AbstractDataBufferDecoder</t>
+  </si>
+  <si>
+    <t>AbstractDecoder</t>
+  </si>
+  <si>
+    <t>AbstractEncoder</t>
+  </si>
+  <si>
+    <t>AbstractSingleValueEncoder</t>
+  </si>
+  <si>
+    <t>ByteArrayDecoder</t>
+  </si>
+  <si>
+    <t>ByteArrayEncoder</t>
+  </si>
+  <si>
+    <t>ByteBufferDecoder</t>
+  </si>
+  <si>
+    <t>ByteBufferEncoder</t>
+  </si>
+  <si>
+    <t>CharSequenceEncoder</t>
+  </si>
+  <si>
+    <t>DataBufferDecoder</t>
+  </si>
+  <si>
+    <t>DataBufferEncoder</t>
+  </si>
+  <si>
+    <t>Hints</t>
+  </si>
+  <si>
+    <t>NettyByteBufDecoder</t>
+  </si>
+  <si>
+    <t>NettyByteBufEncoder</t>
+  </si>
+  <si>
+    <t>ResourceDecoder</t>
+  </si>
+  <si>
+    <t>ResourceEncoder</t>
+  </si>
+  <si>
+    <t>ResourceRegionEncoder</t>
+  </si>
+  <si>
+    <t>StringDecoder</t>
+  </si>
+  <si>
+    <t>CodecException</t>
+  </si>
+  <si>
+    <t>DecodingException</t>
+  </si>
+  <si>
+    <t>EncodingException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.convert</t>
+    </r>
+  </si>
+  <si>
+    <t>ConversionService</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>TypeDescriptor</t>
+  </si>
+  <si>
+    <t>ConversionException</t>
+  </si>
+  <si>
+    <t>ConversionFailedException</t>
+  </si>
+  <si>
+    <t>ConverterNotFoundException</t>
+  </si>
+  <si>
+    <t>org.springframework.core.convert.converter</t>
+  </si>
+  <si>
+    <t>ConditionalConverter</t>
+  </si>
+  <si>
+    <t>ConditionalGenericConverter</t>
+  </si>
+  <si>
+    <t>Converter</t>
+  </si>
+  <si>
+    <t>ConverterFactory</t>
+  </si>
+  <si>
+    <t>ConverterRegistry</t>
+  </si>
+  <si>
+    <t>GenericConverter</t>
+  </si>
+  <si>
+    <t>ConvertingComparator</t>
+  </si>
+  <si>
+    <t>GenericConverter.ConvertiblePair</t>
+  </si>
+  <si>
+    <t>org.springframework.core.convert.support</t>
+  </si>
+  <si>
+    <t>ConfigurableConversionService</t>
+  </si>
+  <si>
+    <t>ConversionServiceFactory</t>
+  </si>
+  <si>
+    <t>ConvertingPropertyEditorAdapter</t>
+  </si>
+  <si>
+    <t>DefaultConversionService</t>
+  </si>
+  <si>
+    <t>GenericConversionService</t>
+  </si>
+  <si>
+    <t>org.springframework.core.env</t>
+  </si>
+  <si>
+    <t>ConfigurableEnvironment</t>
+  </si>
+  <si>
+    <t>ConfigurablePropertyResolver</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>EnvironmentCapable</t>
+  </si>
+  <si>
+    <t>Profiles</t>
+  </si>
+  <si>
+    <t>PropertyResolver</t>
+  </si>
+  <si>
+    <t>PropertySources</t>
+  </si>
+  <si>
+    <t>AbstractEnvironment</t>
+  </si>
+  <si>
+    <t>AbstractPropertyResolver</t>
+  </si>
+  <si>
+    <t>CommandLinePropertySource</t>
+  </si>
+  <si>
+    <t>CompositePropertySource</t>
+  </si>
+  <si>
+    <t>EnumerablePropertySource</t>
+  </si>
+  <si>
+    <t>JOptCommandLinePropertySource</t>
+  </si>
+  <si>
+    <t>MapPropertySource</t>
+  </si>
+  <si>
+    <t>MutablePropertySources</t>
+  </si>
+  <si>
+    <t>PropertiesPropertySource</t>
+  </si>
+  <si>
+    <t>PropertySource</t>
+  </si>
+  <si>
+    <t>PropertySource.StubPropertySource</t>
+  </si>
+  <si>
+    <t>PropertySourcesPropertyResolver</t>
+  </si>
+  <si>
+    <t>SimpleCommandLinePropertySource</t>
+  </si>
+  <si>
+    <t>StandardEnvironment</t>
+  </si>
+  <si>
+    <t>SystemEnvironmentPropertySource</t>
+  </si>
+  <si>
+    <t>MissingRequiredPropertiesException</t>
+  </si>
+  <si>
+    <t>org.springframework.core.io</t>
+  </si>
+  <si>
+    <t>ContextResource</t>
+  </si>
+  <si>
+    <t>InputStreamSource</t>
+  </si>
+  <si>
+    <t>ProtocolResolver</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>ResourceLoader</t>
+  </si>
+  <si>
+    <t>WritableResource</t>
+  </si>
+  <si>
+    <t>AbstractFileResolvingResource</t>
+  </si>
+  <si>
+    <t>AbstractResource</t>
+  </si>
+  <si>
+    <t>ByteArrayResource</t>
+  </si>
+  <si>
+    <t>ClassPathResource</t>
+  </si>
+  <si>
+    <t>ClassRelativeResourceLoader</t>
+  </si>
+  <si>
+    <t>DefaultResourceLoader</t>
+  </si>
+  <si>
+    <t>DefaultResourceLoader.ClassPathContextResource</t>
+  </si>
+  <si>
+    <t>DescriptiveResource</t>
+  </si>
+  <si>
+    <t>FileSystemResource</t>
+  </si>
+  <si>
+    <t>FileSystemResourceLoader</t>
+  </si>
+  <si>
+    <t>FileUrlResource</t>
+  </si>
+  <si>
+    <t>InputStreamResource</t>
+  </si>
+  <si>
+    <t>PathResource</t>
+  </si>
+  <si>
+    <t>ResourceEditor</t>
+  </si>
+  <si>
+    <t>UrlResource</t>
+  </si>
+  <si>
+    <t>VfsResource</t>
+  </si>
+  <si>
+    <t>VfsUtils</t>
+  </si>
+  <si>
+    <t>org.springframework.core.io.buffer</t>
+  </si>
+  <si>
+    <t>DataBuffer</t>
+  </si>
+  <si>
+    <t>DataBufferFactory</t>
+  </si>
+  <si>
+    <t>DataBufferUtils.Matcher</t>
+  </si>
+  <si>
+    <t>PooledDataBuffer</t>
+  </si>
+  <si>
+    <t>DataBufferUtils</t>
+  </si>
+  <si>
+    <t>DataBufferWrapper</t>
+  </si>
+  <si>
+    <t>DefaultDataBuffer</t>
+  </si>
+  <si>
+    <t>DefaultDataBufferFactory</t>
+  </si>
+  <si>
+    <t>LimitedDataBufferList</t>
+  </si>
+  <si>
+    <t>NettyDataBuffer</t>
+  </si>
+  <si>
+    <t>NettyDataBufferFactory</t>
+  </si>
+  <si>
+    <t>DataBufferLimitException</t>
+  </si>
+  <si>
+    <t>org.springframework.core.io.support</t>
+  </si>
+  <si>
+    <t>PropertySourceFactory</t>
+  </si>
+  <si>
+    <t>ResourcePatternResolver</t>
+  </si>
+  <si>
+    <t>DefaultPropertySourceFactory</t>
+  </si>
+  <si>
+    <t>EncodedResource</t>
+  </si>
+  <si>
+    <t>LocalizedResourceHelper</t>
+  </si>
+  <si>
+    <t>PathMatchingResourcePatternResolver</t>
+  </si>
+  <si>
+    <t>PropertiesLoaderSupport</t>
+  </si>
+  <si>
+    <t>PropertiesLoaderUtils</t>
+  </si>
+  <si>
+    <t>ResourceArrayPropertyEditor</t>
+  </si>
+  <si>
+    <t>ResourcePatternUtils</t>
+  </si>
+  <si>
+    <t>ResourcePropertiesPersister</t>
+  </si>
+  <si>
+    <t>ResourcePropertySource</t>
+  </si>
+  <si>
+    <t>ResourceRegion</t>
+  </si>
+  <si>
+    <t>SpringFactoriesLoader</t>
+  </si>
+  <si>
+    <t>org.springframework.core.log</t>
+  </si>
+  <si>
+    <t>LogAccessor</t>
+  </si>
+  <si>
+    <t>LogDelegateFactory</t>
+  </si>
+  <si>
+    <t>LogFormatUtils</t>
+  </si>
+  <si>
+    <t>LogMessage</t>
+  </si>
+  <si>
+    <t>org.springframework.core.metrics</t>
+  </si>
+  <si>
+    <t>ApplicationStartup</t>
+  </si>
+  <si>
+    <t>StartupStep</t>
+  </si>
+  <si>
+    <t>StartupStep.Tag</t>
+  </si>
+  <si>
+    <t>StartupStep.Tags</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.metrics.jfr</t>
+    </r>
+  </si>
+  <si>
+    <t>FlightRecorderApplicationStartup</t>
+  </si>
+  <si>
+    <t>org.springframework.core.serializer</t>
+  </si>
+  <si>
+    <t>Deserializer</t>
+  </si>
+  <si>
+    <t>Serializer</t>
+  </si>
+  <si>
+    <t>DefaultDeserializer</t>
+  </si>
+  <si>
+    <t>DefaultSerializer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.serializer.support</t>
+    </r>
+  </si>
+  <si>
+    <t>DeserializingConverter</t>
+  </si>
+  <si>
+    <t>SerializationDelegate</t>
+  </si>
+  <si>
+    <t>SerializingConverter</t>
+  </si>
+  <si>
+    <t>SerializationFailedException</t>
+  </si>
+  <si>
+    <t>org.springframework.core.style</t>
+  </si>
+  <si>
+    <t>ToStringStyler</t>
+  </si>
+  <si>
+    <t>ValueStyler</t>
+  </si>
+  <si>
+    <t>DefaultToStringStyler</t>
+  </si>
+  <si>
+    <t>DefaultValueStyler</t>
+  </si>
+  <si>
+    <t>StylerUtils</t>
+  </si>
+  <si>
+    <t>ToStringCreator</t>
+  </si>
+  <si>
+    <t>org.springframework.core.task</t>
+  </si>
+  <si>
+    <t>AsyncListenableTaskExecutor</t>
+  </si>
+  <si>
+    <t>AsyncTaskExecutor</t>
+  </si>
+  <si>
+    <t>TaskDecorator</t>
+  </si>
+  <si>
+    <t>TaskExecutor</t>
+  </si>
+  <si>
+    <t>SimpleAsyncTaskExecutor</t>
+  </si>
+  <si>
+    <t>SyncTaskExecutor</t>
+  </si>
+  <si>
+    <t>TaskRejectedException</t>
+  </si>
+  <si>
+    <t>TaskTimeoutException</t>
+  </si>
+  <si>
+    <t>org.springframework.core.task.support</t>
+  </si>
+  <si>
+    <t>ConcurrentExecutorAdapter</t>
+  </si>
+  <si>
+    <t>ExecutorServiceAdapter</t>
+  </si>
+  <si>
+    <t>TaskExecutorAdapter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.type</t>
+    </r>
+  </si>
+  <si>
+    <t>AnnotatedTypeMetadata</t>
+  </si>
+  <si>
+    <t>AnnotationMetadata</t>
+  </si>
+  <si>
+    <t>ClassMetadata</t>
+  </si>
+  <si>
+    <t>MethodMetadata</t>
+  </si>
+  <si>
+    <t>StandardAnnotationMetadata</t>
+  </si>
+  <si>
+    <t>StandardClassMetadata</t>
+  </si>
+  <si>
+    <t>StandardMethodMetadata</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.core.type.classreading</t>
+    </r>
+  </si>
+  <si>
+    <t>MetadataReader</t>
+  </si>
+  <si>
+    <t>MetadataReaderFactory</t>
+  </si>
+  <si>
+    <t>AnnotationMetadataReadingVisitor</t>
+  </si>
+  <si>
+    <t>CachingMetadataReaderFactory</t>
+  </si>
+  <si>
+    <t>MethodMetadataReadingVisitor</t>
+  </si>
+  <si>
+    <t>SimpleMetadataReaderFactory</t>
+  </si>
+  <si>
+    <t>org.springframework.core.type.filter</t>
+  </si>
+  <si>
+    <t>TypeFilter</t>
+  </si>
+  <si>
+    <t>AbstractClassTestingTypeFilter</t>
+  </si>
+  <si>
+    <t>AbstractTypeHierarchyTraversingFilter</t>
+  </si>
+  <si>
+    <t>AnnotationTypeFilter</t>
+  </si>
+  <si>
+    <t>AspectJTypeFilter</t>
+  </si>
+  <si>
+    <t>AssignableTypeFilter</t>
+  </si>
+  <si>
+    <t>RegexPatternTypeFilter</t>
+  </si>
+  <si>
+    <t>org.springframework.dao</t>
+  </si>
+  <si>
+    <t>CannotAcquireLockException</t>
+  </si>
+  <si>
+    <t>CannotSerializeTransactionException</t>
+  </si>
+  <si>
+    <t>CleanupFailureDataAccessException</t>
+  </si>
+  <si>
+    <t>ConcurrencyFailureException</t>
+  </si>
+  <si>
+    <t>DataAccessException</t>
+  </si>
+  <si>
+    <t>DataAccessResourceFailureException</t>
+  </si>
+  <si>
+    <t>DataIntegrityViolationException</t>
+  </si>
+  <si>
+    <t>DataRetrievalFailureException</t>
+  </si>
+  <si>
+    <t>DeadlockLoserDataAccessException</t>
+  </si>
+  <si>
+    <t>DuplicateKeyException</t>
+  </si>
+  <si>
+    <t>EmptyResultDataAccessException</t>
+  </si>
+  <si>
+    <t>IncorrectResultSizeDataAccessException</t>
+  </si>
+  <si>
+    <t>IncorrectUpdateSemanticsDataAccessException</t>
+  </si>
+  <si>
+    <t>InvalidDataAccessApiUsageException</t>
+  </si>
+  <si>
+    <t>InvalidDataAccessResourceUsageException</t>
+  </si>
+  <si>
+    <t>NonTransientDataAccessException</t>
+  </si>
+  <si>
+    <t>NonTransientDataAccessResourceException</t>
+  </si>
+  <si>
+    <t>OptimisticLockingFailureException</t>
+  </si>
+  <si>
+    <t>PermissionDeniedDataAccessException</t>
+  </si>
+  <si>
+    <t>PessimisticLockingFailureException</t>
+  </si>
+  <si>
+    <t>QueryTimeoutException</t>
+  </si>
+  <si>
+    <t>RecoverableDataAccessException</t>
+  </si>
+  <si>
+    <t>TransientDataAccessException</t>
+  </si>
+  <si>
+    <t>TransientDataAccessResourceException</t>
+  </si>
+  <si>
+    <t>TypeMismatchDataAccessException</t>
+  </si>
+  <si>
+    <t>UncategorizedDataAccessException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.dao.annotation</t>
+    </r>
+  </si>
+  <si>
+    <t>PersistenceExceptionTranslationAdvisor</t>
+  </si>
+  <si>
+    <t>PersistenceExceptionTranslationPostProcessor</t>
+  </si>
+  <si>
+    <t>org.springframework.dao.support</t>
+  </si>
+  <si>
+    <t>PersistenceExceptionTranslator</t>
+  </si>
+  <si>
+    <t>ChainedPersistenceExceptionTranslator</t>
+  </si>
+  <si>
+    <t>DaoSupport</t>
+  </si>
+  <si>
+    <t>DataAccessUtils</t>
+  </si>
+  <si>
+    <t>PersistenceExceptionTranslationInterceptor</t>
+  </si>
+  <si>
+    <t>org.springframework.asm</t>
+  </si>
+  <si>
+    <t>Opcodes</t>
+  </si>
+  <si>
+    <t>AnnotationVisitor</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>ByteVector</t>
+  </si>
+  <si>
+    <t>ClassReader</t>
+  </si>
+  <si>
+    <t>ClassVisitor</t>
+  </si>
+  <si>
+    <t>ClassWriter</t>
+  </si>
+  <si>
+    <t>ConstantDynamic</t>
+  </si>
+  <si>
+    <t>FieldVisitor</t>
+  </si>
+  <si>
+    <t>Handle</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>MethodVisitor</t>
+  </si>
+  <si>
+    <t>ModuleVisitor</t>
+  </si>
+  <si>
+    <t>RecordComponentVisitor</t>
+  </si>
+  <si>
+    <t>SpringAsmInfo</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>TypePath</t>
+  </si>
+  <si>
+    <t>TypeReference</t>
+  </si>
+  <si>
+    <t>ClassTooLargeException</t>
+  </si>
+  <si>
+    <t>MethodTooLargeException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.cglib</t>
+    </r>
+  </si>
+  <si>
+    <t>SpringCglibInfo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.cglib.beans</t>
+    </r>
+  </si>
+  <si>
+    <t>BeanCopier</t>
+  </si>
+  <si>
+    <t>BeanCopier.Generator</t>
+  </si>
+  <si>
+    <t>BeanGenerator</t>
+  </si>
+  <si>
+    <t>BeanMap</t>
+  </si>
+  <si>
+    <t>BeanMap.Generator</t>
+  </si>
+  <si>
+    <t>BulkBean</t>
+  </si>
+  <si>
+    <t>BulkBean.Generator</t>
+  </si>
+  <si>
+    <t>FixedKeySet</t>
+  </si>
+  <si>
+    <t>ImmutableBean</t>
+  </si>
+  <si>
+    <t>ImmutableBean.Generator</t>
+  </si>
+  <si>
+    <t>BulkBeanException</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.cglib.core</t>
+    </r>
+  </si>
+  <si>
+    <t>AbstractClassGenerator</t>
+  </si>
+  <si>
+    <t>AbstractClassGenerator.ClassLoaderData</t>
+  </si>
+  <si>
+    <t>AbstractClassGenerator.Source</t>
+  </si>
+  <si>
+    <t>ClassLoaderAwareGeneratorStrategy</t>
+  </si>
+  <si>
+    <t>KeyFactory</t>
+  </si>
+  <si>
+    <t>KeyFactory.Generator</t>
+  </si>
+  <si>
+    <t>ReflectUtils</t>
+  </si>
+  <si>
+    <t>SpringNamingPolicy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.cglib.proxy</t>
+    </r>
+  </si>
+  <si>
+    <t>Enhancer.EnhancerKey</t>
+  </si>
+  <si>
+    <t>Enhancer</t>
+  </si>
+  <si>
+    <t>MethodProxy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.lang</t>
+    </r>
+  </si>
+  <si>
+    <t>NonNull</t>
+  </si>
+  <si>
+    <t>NonNullApi</t>
+  </si>
+  <si>
+    <t>NonNullFields</t>
+  </si>
+  <si>
+    <t>Nullable</t>
+  </si>
+  <si>
+    <t>UsesJava7</t>
+  </si>
+  <si>
+    <t>UsesJava8</t>
+  </si>
+  <si>
+    <t>UsesSunHttpServer</t>
+  </si>
+  <si>
+    <t>UsesSunMisc</t>
+  </si>
+  <si>
+    <t>org.springframework.expression</t>
+  </si>
+  <si>
+    <t>BeanResolver</t>
+  </si>
+  <si>
+    <t>ConstructorExecutor</t>
+  </si>
+  <si>
+    <t>ConstructorResolver</t>
+  </si>
+  <si>
+    <t>EvaluationContext</t>
+  </si>
+  <si>
+    <t>Expression</t>
+  </si>
+  <si>
+    <t>ExpressionParser</t>
+  </si>
+  <si>
+    <t>MethodExecutor</t>
+  </si>
+  <si>
+    <t>MethodFilter</t>
+  </si>
+  <si>
+    <t>MethodResolver</t>
+  </si>
+  <si>
+    <t>OperatorOverloader</t>
+  </si>
+  <si>
+    <t>ParserContext</t>
+  </si>
+  <si>
+    <t>PropertyAccessor</t>
+  </si>
+  <si>
+    <t>TypeComparator</t>
+  </si>
+  <si>
+    <t>TypeConverter</t>
+  </si>
+  <si>
+    <t>TypeLocator</t>
+  </si>
+  <si>
+    <t>TypedValue</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>AccessException</t>
+  </si>
+  <si>
+    <t>EvaluationException</t>
+  </si>
+  <si>
+    <t>ExpressionException</t>
+  </si>
+  <si>
+    <t>ExpressionInvocationTargetException</t>
+  </si>
+  <si>
+    <t>ParseException</t>
+  </si>
+  <si>
+    <t>org.springframework.expression.common</t>
+  </si>
+  <si>
+    <t>CompositeStringExpression</t>
+  </si>
+  <si>
+    <t>ExpressionUtils</t>
+  </si>
+  <si>
+    <t>LiteralExpression</t>
+  </si>
+  <si>
+    <t>TemplateAwareExpressionParser</t>
+  </si>
+  <si>
+    <t>TemplateParserContext</t>
+  </si>
+  <si>
+    <t>org.springframework.expression.spel</t>
+  </si>
+  <si>
+    <t>CodeFlow.ClinitAdder</t>
+  </si>
+  <si>
+    <t>CodeFlow.FieldAdder</t>
+  </si>
+  <si>
+    <t>CompilablePropertyAccessor</t>
+  </si>
+  <si>
+    <t>SpelNode</t>
+  </si>
+  <si>
+    <t>CodeFlow</t>
+  </si>
+  <si>
+    <t>CompiledExpression</t>
+  </si>
+  <si>
+    <t>ExpressionState</t>
+  </si>
+  <si>
+    <t>SpelParserConfiguration</t>
+  </si>
+  <si>
+    <t>SpelCompilerMode</t>
+  </si>
+  <si>
+    <t>SpelMessage</t>
+  </si>
+  <si>
+    <t>SpelMessage.Kind</t>
+  </si>
+  <si>
+    <t>InternalParseException</t>
+  </si>
+  <si>
+    <t>SpelEvaluationException</t>
+  </si>
+  <si>
+    <t>SpelParseException</t>
+  </si>
+  <si>
+    <t>org.springframework.expression.spel.ast</t>
+  </si>
+  <si>
+    <t>ValueRef</t>
+  </si>
+  <si>
+    <t>Assign</t>
+  </si>
+  <si>
+    <t>AstUtils</t>
+  </si>
+  <si>
+    <t>BeanReference</t>
+  </si>
+  <si>
+    <t>BooleanLiteral</t>
+  </si>
+  <si>
+    <t>CompoundExpression</t>
+  </si>
+  <si>
+    <t>ConstructorReference</t>
+  </si>
+  <si>
+    <t>Elvis</t>
+  </si>
+  <si>
+    <t>FloatLiteral</t>
+  </si>
+  <si>
+    <t>FunctionReference</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>Indexer</t>
+  </si>
+  <si>
+    <t>InlineList</t>
+  </si>
+  <si>
+    <t>InlineMap</t>
+  </si>
+  <si>
+    <t>IntLiteral</t>
+  </si>
+  <si>
+    <t>Literal</t>
+  </si>
+  <si>
+    <t>LongLiteral</t>
+  </si>
+  <si>
+    <t>MethodReference</t>
+  </si>
+  <si>
+    <t>NullLiteral</t>
+  </si>
+  <si>
+    <t>OpAnd</t>
+  </si>
+  <si>
+    <t>OpDec</t>
+  </si>
+  <si>
+    <t>OpDivide</t>
+  </si>
+  <si>
+    <t>OpEQ</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Operator.DescriptorComparison</t>
+  </si>
+  <si>
+    <t>OperatorBetween</t>
+  </si>
+  <si>
+    <t>OperatorInstanceof</t>
+  </si>
+  <si>
+    <t>OperatorMatches</t>
+  </si>
+  <si>
+    <t>OperatorNot</t>
+  </si>
+  <si>
+    <t>OperatorPower</t>
+  </si>
+  <si>
+    <t>OpGE</t>
+  </si>
+  <si>
+    <t>OpGT</t>
+  </si>
+  <si>
+    <t>OpInc</t>
+  </si>
+  <si>
+    <t>OpLE</t>
+  </si>
+  <si>
+    <t>OpLT</t>
+  </si>
+  <si>
+    <t>OpMinus</t>
+  </si>
+  <si>
+    <t>OpModulus</t>
+  </si>
+  <si>
+    <t>OpMultiply</t>
+  </si>
+  <si>
+    <t>OpNE</t>
+  </si>
+  <si>
+    <t>OpOr</t>
+  </si>
+  <si>
+    <t>OpPlus</t>
+  </si>
+  <si>
+    <t>Projection</t>
+  </si>
+  <si>
+    <t>PropertyOrFieldReference</t>
+  </si>
+  <si>
+    <t>QualifiedIdentifier</t>
+  </si>
+  <si>
+    <t>RealLiteral</t>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>SpelNodeImpl</t>
+  </si>
+  <si>
+    <t>StringLiteral</t>
+  </si>
+  <si>
+    <t>Ternary</t>
+  </si>
+  <si>
+    <t>ValueRef.NullValueRef</t>
+  </si>
+  <si>
+    <t>ValueRef.TypedValueHolderValueRef</t>
+  </si>
+  <si>
+    <t>VariableReference</t>
+  </si>
+  <si>
+    <t>TypeCode</t>
+  </si>
+  <si>
+    <t>org.springframework.expression.spel.standard</t>
+  </si>
+  <si>
+    <t>SpelCompiler</t>
+  </si>
+  <si>
+    <t>SpelExpression</t>
+  </si>
+  <si>
+    <t>SpelExpressionParser</t>
+  </si>
+  <si>
+    <t>org.springframework.expression.spel.support</t>
+  </si>
+  <si>
+    <t>BooleanTypedValue</t>
+  </si>
+  <si>
+    <t>DataBindingMethodResolver</t>
+  </si>
+  <si>
+    <t>DataBindingPropertyAccessor</t>
+  </si>
+  <si>
+    <t>ReflectionHelper</t>
+  </si>
+  <si>
+    <t>ReflectiveConstructorExecutor</t>
+  </si>
+  <si>
+    <t>ReflectiveConstructorResolver</t>
+  </si>
+  <si>
+    <t>ReflectiveMethodExecutor</t>
+  </si>
+  <si>
+    <t>ReflectiveMethodResolver</t>
+  </si>
+  <si>
+    <t>ReflectivePropertyAccessor</t>
+  </si>
+  <si>
+    <t>ReflectivePropertyAccessor.OptimalPropertyAccessor</t>
+  </si>
+  <si>
+    <t>SimpleEvaluationContext</t>
+  </si>
+  <si>
+    <t>SimpleEvaluationContext.Builder</t>
+  </si>
+  <si>
+    <t>StandardEvaluationContext</t>
+  </si>
+  <si>
+    <t>StandardOperatorOverloader</t>
+  </si>
+  <si>
+    <t>StandardTypeComparator</t>
+  </si>
+  <si>
+    <t>StandardTypeConverter</t>
+  </si>
+  <si>
+    <t>StandardTypeLocator</t>
+  </si>
+  <si>
+    <t>org.springframework.ejb.access</t>
+  </si>
+  <si>
+    <t>AbstractRemoteSlsbInvokerInterceptor</t>
+  </si>
+  <si>
+    <t>AbstractSlsbInvokerInterceptor</t>
+  </si>
+  <si>
+    <t>LocalSlsbInvokerInterceptor</t>
+  </si>
+  <si>
+    <t>LocalStatelessSessionProxyFactoryBean</t>
+  </si>
+  <si>
+    <t>SimpleRemoteSlsbInvokerInterceptor</t>
+  </si>
+  <si>
+    <t>SimpleRemoteStatelessSessionProxyFactoryBean</t>
+  </si>
+  <si>
+    <t>EjbAccessException</t>
+  </si>
+  <si>
+    <t>org.springframework.ejb.config</t>
+  </si>
+  <si>
+    <t>JeeNamespaceHandler</t>
+  </si>
+  <si>
+    <t>org.springframework.format</t>
+  </si>
+  <si>
+    <t>AnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>Formatter</t>
+  </si>
+  <si>
+    <t>FormatterRegistrar</t>
+  </si>
+  <si>
+    <t>FormatterRegistry</t>
+  </si>
+  <si>
+    <t>Parser</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>org.springframework.format.annotation</t>
+  </si>
+  <si>
+    <t>DateTimeFormat.ISO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NumberFormat.Style</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DateTimeFormat</t>
+    </r>
+  </si>
+  <si>
+    <t>NumberFormat</t>
+  </si>
+  <si>
+    <t>org.springframework.format.datetime</t>
+  </si>
+  <si>
+    <t>DateFormatter</t>
+  </si>
+  <si>
+    <t>DateFormatterRegistrar</t>
+  </si>
+  <si>
+    <t>DateTimeFormatAnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>org.springframework.format.datetime.joda</t>
+  </si>
+  <si>
+    <t>DateTimeFormatterFactory</t>
+  </si>
+  <si>
+    <t>DateTimeFormatterFactoryBean</t>
+  </si>
+  <si>
+    <t>DateTimeParser</t>
+  </si>
+  <si>
+    <t>JodaDateTimeFormatAnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>JodaTimeContext</t>
+  </si>
+  <si>
+    <t>JodaTimeContextHolder</t>
+  </si>
+  <si>
+    <t>JodaTimeFormatterRegistrar</t>
+  </si>
+  <si>
+    <t>LocalDateParser</t>
+  </si>
+  <si>
+    <t>LocalDateTimeParser</t>
+  </si>
+  <si>
+    <t>LocalTimeParser</t>
+  </si>
+  <si>
+    <t>MillisecondInstantPrinter</t>
+  </si>
+  <si>
+    <t>ReadableInstantPrinter</t>
+  </si>
+  <si>
+    <t>ReadablePartialPrinter</t>
+  </si>
+  <si>
+    <t>org.springframework.format.datetime.standard</t>
+  </si>
+  <si>
+    <t>DateTimeContext</t>
+  </si>
+  <si>
+    <t>DateTimeContextHolder</t>
+  </si>
+  <si>
+    <t>DateTimeFormatterRegistrar</t>
+  </si>
+  <si>
+    <t>InstantFormatter</t>
+  </si>
+  <si>
+    <t>Jsr310DateTimeFormatAnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>TemporalAccessorParser</t>
+  </si>
+  <si>
+    <t>TemporalAccessorPrinter</t>
+  </si>
+  <si>
+    <t>org.springframework.format.number</t>
+  </si>
+  <si>
+    <t>AbstractNumberFormatter</t>
+  </si>
+  <si>
+    <t>CurrencyStyleFormatter</t>
+  </si>
+  <si>
+    <t>NumberFormatAnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>NumberStyleFormatter</t>
+  </si>
+  <si>
+    <t>PercentStyleFormatter</t>
+  </si>
+  <si>
+    <t>org.springframework.format.number.money</t>
+  </si>
+  <si>
+    <t>CurrencyUnitFormatter</t>
+  </si>
+  <si>
+    <t>Jsr354NumberFormatAnnotationFormatterFactory</t>
+  </si>
+  <si>
+    <t>MonetaryAmountFormatter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.format.support</t>
+    </r>
+  </si>
+  <si>
+    <t>DefaultFormattingConversionService</t>
+  </si>
+  <si>
+    <t>FormatterPropertyEditorAdapter</t>
+  </si>
+  <si>
+    <t>FormattingConversionService</t>
+  </si>
+  <si>
+    <t>FormattingConversionServiceFactoryBean</t>
   </si>
 </sst>
 </file>
@@ -170,13 +1808,58 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.75"/>
+      <color rgb="FF353833"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF353833"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF4A6782"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -323,12 +2006,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -631,10 +2320,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -643,139 +2332,163 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1346,4 +3059,2919 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A463"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="58.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" ht="25.2" spans="1:1">
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" ht="25.2" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="286" ht="19.2" spans="1:1">
+      <c r="A286" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" t="s">
+        <v>296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:A107"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="32.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1">
+      <c r="A3" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" ht="25.2" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" ht="25.2" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" ht="31.2" spans="1:1">
+      <c r="A38" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A100" r:id="rId1" display="NonNull" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNull.html"/>
+    <hyperlink ref="A101" r:id="rId2" display="NonNullApi" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNullApi.html"/>
+    <hyperlink ref="A102" r:id="rId3" display="NonNullFields" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNullFields.html"/>
+    <hyperlink ref="A103" r:id="rId4" display="Nullable" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/Nullable.html"/>
+    <hyperlink ref="A104" r:id="rId5" display="UsesJava7" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesJava7.html"/>
+    <hyperlink ref="A105" r:id="rId6" display="UsesJava8" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesJava8.html"/>
+    <hyperlink ref="A106" r:id="rId7" display="UsesSunHttpServer" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesSunHttpServer.html"/>
+    <hyperlink ref="A107" r:id="rId8" display="UsesSunMisc" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesSunMisc.html"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A176"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="54.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="55.2" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" ht="25.2" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="29" ht="25.2" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>473</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:A121"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="33.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="55.2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="13" ht="25.2" spans="1:1">
+      <c r="A13" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="18" ht="55.2" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="38" ht="27.6" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="59" ht="27.6" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="78" ht="27.6" spans="1:1">
+      <c r="A78" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="104" ht="27.6" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>536</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/java/spring/org.springframework.core.xlsx
+++ b/java/spring/org.springframework.core.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21648" windowHeight="9155" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="22368" windowHeight="9564"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.core" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="538">
   <si>
     <t>AliasRegistry</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>MethodParameter</t>
+  </si>
+  <si>
+    <t>getParameterType()方法</t>
   </si>
   <si>
     <t>NamedInheritableThreadLocal&lt;T&gt;</t>
@@ -2809,8 +2812,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="53.3333333333333" customWidth="1"/>
   </cols>
@@ -2925,134 +2928,137 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3072,1457 +3078,1457 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" ht="25.2" spans="1:1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" ht="25.2" spans="1:1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="286" ht="19.2" spans="1:1">
       <c r="A286" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="447" spans="1:1">
       <c r="A447" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="451" spans="1:1">
       <c r="A451" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="453" spans="1:1">
       <c r="A453" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="460" spans="1:1">
       <c r="A460" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="461" spans="1:1">
       <c r="A461" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="463" spans="1:1">
       <c r="A463" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4542,337 +4548,337 @@
   <sheetData>
     <row r="3" spans="1:1">
       <c r="A3" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" ht="25.2" spans="1:1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="29" ht="25.2" spans="1:1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" ht="31.2" spans="1:1">
       <c r="A38" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4900,679 +4906,679 @@
     <col min="1" max="1" width="54.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="55.2" spans="1:1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="3" ht="25.2" spans="1:1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="29" ht="25.2" spans="1:1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -5590,384 +5596,384 @@
     <col min="1" max="1" width="33.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="55.2" spans="1:1">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="13" ht="25.2" spans="1:1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="18" ht="55.2" spans="1:1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" ht="27.6" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" ht="27.6" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="78" ht="27.6" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="104" ht="27.6" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/java/spring/org.springframework.core.xlsx
+++ b/java/spring/org.springframework.core.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.core" sheetId="2" r:id="rId1"/>
@@ -18,23 +18,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="577">
   <si>
     <t>AliasRegistry</t>
   </si>
   <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>void registerAlias(String name, String alias)
+void removeAlias(String alias)</t>
+  </si>
+  <si>
     <t>AttributeAccessor</t>
   </si>
   <si>
     <t>AttributeAccessorSupport</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0033B3"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>abstract</t>
+    </r>
+  </si>
+  <si>
     <t>BridgeMethodResolver</t>
   </si>
   <si>
+    <t>final类，一堆static方法</t>
+  </si>
+  <si>
     <t>CollectionFactory</t>
   </si>
   <si>
+    <t>final类，有两个map属性，工具类，创建map，list的</t>
+  </si>
+  <si>
     <t>ConfigurableObjectInputStream</t>
   </si>
   <si>
@@ -53,12 +77,25 @@
     <t>DecoratingClassLoader</t>
   </si>
   <si>
+    <t>abstract</t>
+  </si>
+  <si>
+    <t>Set&lt;String&gt; excludedPackages
+Set&lt;String&gt; excludedClasses</t>
+  </si>
+  <si>
     <t>DecoratingProxy</t>
   </si>
   <si>
+    <t>Class&lt;?&gt; getDecoratedClass()</t>
+  </si>
+  <si>
     <t>DefaultParameterNameDiscoverer</t>
   </si>
   <si>
+    <t>extends PrioritizedParameterNameDiscoverer</t>
+  </si>
+  <si>
     <t>ExceptionDepthComparator</t>
   </si>
   <si>
@@ -68,6 +105,9 @@
     <t>InfrastructureProxy</t>
   </si>
   <si>
+    <t>Object getWrappedObject()</t>
+  </si>
+  <si>
     <t>KotlinDetector</t>
   </si>
   <si>
@@ -77,9 +117,15 @@
     <t>LocalVariableTableParameterNameDiscoverer</t>
   </si>
   <si>
+    <t>工具类，用于获取方法参数的名称。</t>
+  </si>
+  <si>
     <t>MethodClassKey</t>
   </si>
   <si>
+    <t xml:space="preserve">final class MethodClassKey implements Comparable&lt;MethodClassKey&gt; </t>
+  </si>
+  <si>
     <t>MethodIntrospector</t>
   </si>
   <si>
@@ -104,6 +150,9 @@
     <t>NestedCheckedException</t>
   </si>
   <si>
+    <t>exception</t>
+  </si>
+  <si>
     <t>NestedExceptionUtils</t>
   </si>
   <si>
@@ -113,12 +162,18 @@
     <t>OrderComparator</t>
   </si>
   <si>
+    <t>工具类，用于对实现了 Ordered 接口的对象进行排序。</t>
+  </si>
+  <si>
     <t>OrderComparator.OrderSourceProvider</t>
   </si>
   <si>
     <t>Ordered</t>
   </si>
   <si>
+    <t>int getOrder()</t>
+  </si>
+  <si>
     <t>OverridingClassLoader</t>
   </si>
   <si>
@@ -128,15 +183,28 @@
     <t>ParameterNameDiscoverer</t>
   </si>
   <si>
+    <t>String[] getParameterNames(Method method)
+String[] getParameterNames(Constructor&lt;?&gt; ctor)</t>
+  </si>
+  <si>
     <t>PrioritizedParameterNameDiscoverer</t>
   </si>
   <si>
+    <t>实现了ParameterNameDiscoverer</t>
+  </si>
+  <si>
     <t>PriorityOrdered</t>
   </si>
   <si>
+    <t>PriorityOrdered extends Ordered</t>
+  </si>
+  <si>
     <t>ReactiveAdapter</t>
   </si>
   <si>
+    <t>5.0才有</t>
+  </si>
+  <si>
     <t>ReactiveAdapterRegistry</t>
   </si>
   <si>
@@ -155,6 +223,9 @@
     <t>SimpleAliasRegistry</t>
   </si>
   <si>
+    <t>implements AliasRegistry</t>
+  </si>
+  <si>
     <t>SmartClassLoader</t>
   </si>
   <si>
@@ -162,6 +233,9 @@
   </si>
   <si>
     <t>SpringVersion</t>
+  </si>
+  <si>
+    <t>getVersion()方法返回 5.2.9.RELEASE</t>
   </si>
   <si>
     <t>StandardReflectionParameterNameDiscoverer</t>
@@ -432,6 +506,28 @@
     <t>ConfigurableConversionService</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AbstractConditionalEnumConverter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ArrayToArrayConverter</t>
+    </r>
+  </si>
+  <si>
     <t>ConversionServiceFactory</t>
   </si>
   <si>
@@ -444,6 +540,10 @@
     <t>GenericConversionService</t>
   </si>
   <si>
+    <t>GenericConversionService 是 Spring Framework 中的一个通用类型转换服务，用于将一个对象转换为另外一个类型。
+在 Spring Framework 中，类型转换是一种常见的操作，例如将字符串转换为数字，将日期转换为字符串等。GenericConversionService 提供了一个通用的类型转换服务，可以将一个对象转换为另外一个类型。GenericConversionService 支持自定义类型转换器，可以通过注册自定义的 Converter 或 ConverterFactory 来扩展类型转换服务的功能。</t>
+  </si>
+  <si>
     <t>org.springframework.core.env</t>
   </si>
   <si>
@@ -525,6 +625,9 @@
     <t>InputStreamSource</t>
   </si>
   <si>
+    <t>接口</t>
+  </si>
+  <si>
     <t>ProtocolResolver</t>
   </si>
   <si>
@@ -549,6 +652,9 @@
     <t>ClassPathResource</t>
   </si>
   <si>
+    <t>实现Resource接口</t>
+  </si>
+  <si>
     <t>ClassRelativeResourceLoader</t>
   </si>
   <si>
@@ -597,6 +703,10 @@
     <t>DataBufferFactory</t>
   </si>
   <si>
+    <t>实现类：NettyDataBufferFactory
+DefaultDataBufferFactory</t>
+  </si>
+  <si>
     <t>DataBufferUtils.Matcher</t>
   </si>
   <si>
@@ -612,6 +722,9 @@
     <t>DefaultDataBuffer</t>
   </si>
   <si>
+    <t>`5.0</t>
+  </si>
+  <si>
     <t>DefaultDataBufferFactory</t>
   </si>
   <si>
@@ -633,28 +746,54 @@
     <t>PropertySourceFactory</t>
   </si>
   <si>
+    <t>PropertySource&lt;?&gt; createPropertySource(@Nullable String name, EncodedResource resource)
+接口实现类DefaultPropertySourceFactory</t>
+  </si>
+  <si>
     <t>ResourcePatternResolver</t>
   </si>
   <si>
+    <t>Resource[] getResources(String locationPattern)</t>
+  </si>
+  <si>
     <t>DefaultPropertySourceFactory</t>
   </si>
   <si>
+    <t>实现了PropertySourceFactory接口</t>
+  </si>
+  <si>
     <t>EncodedResource</t>
   </si>
   <si>
     <t>LocalizedResourceHelper</t>
   </si>
   <si>
+    <t>Resource findLocalizedResource(String name, String extension, @Nullable Locale locale)</t>
+  </si>
+  <si>
     <t>PathMatchingResourcePatternResolver</t>
   </si>
   <si>
+    <t>实现ResourcePatternResolver 接口
+Resource[] getResources(String locationPattern)</t>
+  </si>
+  <si>
     <t>PropertiesLoaderSupport</t>
   </si>
   <si>
+    <t xml:space="preserve">子类PropertiesFactoryBean
+PropertyResourceConfigurer
+PropertyOverrideConfigurer
+</t>
+  </si>
+  <si>
     <t>PropertiesLoaderUtils</t>
   </si>
   <si>
     <t>ResourceArrayPropertyEditor</t>
+  </si>
+  <si>
+    <t>继承PropertyEditorSupport接口</t>
   </si>
   <si>
     <t>ResourcePatternUtils</t>
@@ -728,7 +867,15 @@
     <t>DefaultDeserializer</t>
   </si>
   <si>
+    <t>实现Deserializer接口
+public Object deserialize(InputStream inputStream)</t>
+  </si>
+  <si>
     <t>DefaultSerializer</t>
+  </si>
+  <si>
+    <t>实现Serializer接口
+void serialize(T object, OutputStream outputStream)</t>
   </si>
   <si>
     <r>
@@ -745,7 +892,13 @@
     <t>DeserializingConverter</t>
   </si>
   <si>
+    <t>implements Converter&lt;byte[], Object&gt;</t>
+  </si>
+  <si>
     <t>SerializationDelegate</t>
+  </si>
+  <si>
+    <t>`4.3  SerializationDelegate implements Serializer&lt;Object&gt;, Deserializer&lt;Object&gt;</t>
   </si>
   <si>
     <t>SerializingConverter</t>
@@ -1811,7 +1964,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1862,6 +2015,12 @@
       <sz val="15"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0033B3"/>
+      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2009,7 +2168,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2019,6 +2178,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2323,10 +2500,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2335,34 +2512,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2374,98 +2548,101 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2490,8 +2667,26 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2812,253 +3007,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="53.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="43.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="84" customHeight="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" ht="15.6" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:3">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>18</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>42</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>49</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="43.2" spans="1:3">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>50</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>62</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>65</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3070,1465 +3363,1539 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A463"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C465"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="58.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="52.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="7" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>118</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" ht="15.6" spans="1:1">
+      <c r="A120" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" ht="15.6" spans="1:1">
+      <c r="A121" s="8" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="2" t="s">
-        <v>50</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="125" ht="158.4" spans="1:3">
+      <c r="A125" t="s">
+        <v>143</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>123</v>
+      <c r="A132" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>128</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="2" t="s">
-        <v>56</v>
+      <c r="A140" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>130</v>
+      <c r="A142" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>143</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="2" t="s">
-        <v>70</v>
+      <c r="A158" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="2" t="s">
-        <v>50</v>
+      <c r="A160" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>147</v>
+      <c r="A171" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>149</v>
+        <v>171</v>
+      </c>
+      <c r="B174" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>151</v>
+        <v>174</v>
+      </c>
+      <c r="B176" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="178" spans="1:1">
-      <c r="A178" s="2" t="s">
-        <v>56</v>
+      <c r="A178" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
+      <c r="A180" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
+        <v>177</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>155</v>
+        <v>178</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>157</v>
+        <v>180</v>
+      </c>
+      <c r="B185" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" s="2" t="s">
-        <v>50</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>171</v>
+      <c r="A206" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="209" ht="100.8" spans="1:3">
       <c r="A209" t="s">
-        <v>173</v>
+        <v>197</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="211" spans="1:1">
-      <c r="A211" s="2" t="s">
-        <v>56</v>
+      <c r="A211" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" t="s">
-        <v>175</v>
+      <c r="A213" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>178</v>
+        <v>203</v>
+      </c>
+      <c r="C217" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>180</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="2" t="s">
-        <v>70</v>
+      <c r="A221" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="2" t="s">
-        <v>50</v>
+      <c r="A223" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" s="2" t="s">
-        <v>56</v>
+      <c r="A235" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="237" ht="43.2" spans="1:3">
+      <c r="A237" t="s">
+        <v>211</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>213</v>
+      </c>
+      <c r="C238" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
+      <c r="A240" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>187</v>
+        <v>215</v>
+      </c>
+      <c r="C242" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
+        <v>218</v>
+      </c>
+      <c r="C244" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="245" ht="28.8" spans="1:3">
       <c r="A245" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
+        <v>220</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="246" ht="57.6" spans="1:3">
       <c r="A246" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
+        <v>222</v>
+      </c>
+      <c r="B246" t="s">
+        <v>16</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
+        <v>224</v>
+      </c>
+      <c r="B247" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>193</v>
+        <v>225</v>
+      </c>
+      <c r="C248" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="2" t="s">
-        <v>56</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="258" spans="1:1">
-      <c r="A258" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" t="s">
-        <v>199</v>
+      <c r="A258" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1">
-      <c r="A267" s="2" t="s">
-        <v>50</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" t="s">
-        <v>204</v>
+      <c r="A269" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1">
-      <c r="A280" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="286" ht="19.2" spans="1:1">
-      <c r="A286" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" s="2" t="s">
-        <v>50</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="288" ht="19.2" spans="1:1">
+      <c r="A288" s="10" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="290" spans="1:1">
-      <c r="A290" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1">
-      <c r="A291" t="s">
-        <v>211</v>
+      <c r="A290" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="2" t="s">
-        <v>56</v>
+      <c r="A293" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1">
-      <c r="A296" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1">
-      <c r="A302" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1">
-      <c r="A303" s="2" t="s">
-        <v>56</v>
+      <c r="A295" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="297" ht="28.8" spans="1:3">
+      <c r="A297" t="s">
+        <v>247</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="298" ht="109" customHeight="1" spans="1:3">
+      <c r="A298" t="s">
+        <v>249</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="305" spans="1:1">
-      <c r="A305" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1">
-      <c r="A306" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1">
+      <c r="A305" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>217</v>
+        <v>252</v>
+      </c>
+      <c r="C307" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>254</v>
+      </c>
+      <c r="C308" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="2" t="s">
-        <v>70</v>
+      <c r="A309" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1">
-      <c r="A314" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1">
-      <c r="A315" s="2" t="s">
-        <v>50</v>
+      <c r="A311" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="317" spans="1:1">
-      <c r="A317" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1">
-      <c r="A318" t="s">
-        <v>221</v>
+      <c r="A317" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="320" spans="1:1">
-      <c r="A320" s="2" t="s">
-        <v>56</v>
+      <c r="A320" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="322" spans="1:1">
-      <c r="A322" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1">
-      <c r="A323" t="s">
-        <v>223</v>
+      <c r="A322" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1">
-      <c r="A331" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1">
-      <c r="A332" s="2" t="s">
-        <v>50</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="1" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="334" spans="1:1">
-      <c r="A334" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1">
-      <c r="A335" t="s">
-        <v>228</v>
+      <c r="A334" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>230</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="339" spans="1:1">
-      <c r="A339" s="2" t="s">
-        <v>56</v>
+      <c r="A339" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="341" spans="1:1">
-      <c r="A341" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1">
-      <c r="A342" t="s">
-        <v>232</v>
+      <c r="A341" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="344" spans="1:1">
-      <c r="A344" s="2" t="s">
-        <v>70</v>
+      <c r="A344" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="346" spans="1:1">
-      <c r="A346" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1">
-      <c r="A347" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1">
-      <c r="A353" s="2" t="s">
-        <v>56</v>
+      <c r="A346" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="355" spans="1:1">
-      <c r="A355" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" t="s">
-        <v>237</v>
+      <c r="A355" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1">
-      <c r="A362" s="3" t="s">
-        <v>239</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="364" spans="1:1">
-      <c r="A364" s="2" t="s">
-        <v>50</v>
+      <c r="A364" s="3" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="366" spans="1:1">
-      <c r="A366" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1">
-      <c r="A367" t="s">
-        <v>241</v>
+      <c r="A366" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>243</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="371" spans="1:1">
-      <c r="A371" s="2" t="s">
-        <v>56</v>
+      <c r="A371" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="373" spans="1:1">
-      <c r="A373" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="374" spans="1:1">
-      <c r="A374" t="s">
-        <v>245</v>
+      <c r="A373" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="379" spans="1:1">
-      <c r="A379" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="380" spans="1:1">
-      <c r="A380" s="2" t="s">
-        <v>50</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="382" spans="1:1">
-      <c r="A382" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="383" spans="1:1">
-      <c r="A383" t="s">
-        <v>249</v>
+      <c r="A382" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="385" spans="1:1">
-      <c r="A385" s="2" t="s">
-        <v>56</v>
+      <c r="A385" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="387" spans="1:1">
-      <c r="A387" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1">
-      <c r="A388" t="s">
-        <v>251</v>
+      <c r="A387" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="393" spans="1:1">
-      <c r="A393" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1">
-      <c r="A394" s="2" t="s">
-        <v>50</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="396" spans="1:1">
-      <c r="A396" t="s">
-        <v>255</v>
+      <c r="A396" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="398" spans="1:1">
-      <c r="A398" s="2" t="s">
-        <v>56</v>
+      <c r="A398" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="400" spans="1:1">
-      <c r="A400" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="401" spans="1:1">
-      <c r="A401" t="s">
-        <v>257</v>
+      <c r="A400" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1">
-      <c r="A412" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="413" spans="1:1">
-      <c r="A413" s="2" t="s">
-        <v>70</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="415" spans="1:1">
-      <c r="A415" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1">
-      <c r="A416" t="s">
-        <v>264</v>
+      <c r="A415" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>284</v>
+        <v>321</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>285</v>
+        <v>322</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="447" spans="1:1">
-      <c r="A447" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="448" spans="1:1">
-      <c r="A448" s="2" t="s">
-        <v>56</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="450" spans="1:1">
-      <c r="A450" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1">
-      <c r="A451" t="s">
-        <v>291</v>
+      <c r="A450" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="453" spans="1:1">
-      <c r="A453" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1">
-      <c r="A454" s="2" t="s">
-        <v>50</v>
+      <c r="A453" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="1" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="456" spans="1:1">
-      <c r="A456" t="s">
-        <v>293</v>
+      <c r="A456" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="458" spans="1:1">
-      <c r="A458" s="2" t="s">
-        <v>56</v>
+      <c r="A458" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="460" spans="1:1">
-      <c r="A460" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="461" spans="1:1">
-      <c r="A461" t="s">
-        <v>295</v>
+      <c r="A460" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
     </row>
     <row r="463" spans="1:1">
       <c r="A463" t="s">
-        <v>297</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4548,337 +4915,337 @@
   <sheetData>
     <row r="3" spans="1:1">
       <c r="A3" s="4" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" ht="31.2" spans="1:1">
       <c r="A38" s="5" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>322</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>345</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="6" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="6" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="6" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="6" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="6" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="6" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="6" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4908,677 +5275,677 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -5598,382 +5965,382 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" ht="27.6" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
     </row>
     <row r="59" ht="27.6" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
     </row>
     <row r="78" ht="27.6" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>516</v>
+        <v>555</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>518</v>
+        <v>557</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>525</v>
+        <v>564</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>528</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" ht="27.6" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>532</v>
+        <v>571</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="3" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>537</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/java/spring/org.springframework.core.xlsx
+++ b/java/spring/org.springframework.core.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.core" sheetId="2" r:id="rId1"/>
@@ -2642,7 +2642,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2666,9 +2666,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3019,10 +3016,10 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3030,7 +3027,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3038,7 +3035,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3090,7 +3087,7 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3098,7 +3095,7 @@
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -3127,7 +3124,7 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -3171,7 +3168,7 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>34</v>
       </c>
       <c r="C23" t="s">
@@ -3197,7 +3194,7 @@
       <c r="A27" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3210,7 +3207,7 @@
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3231,7 +3228,7 @@
       <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
@@ -3247,7 +3244,7 @@
       <c r="A34" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3255,10 +3252,10 @@
       <c r="A35" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3316,7 +3313,7 @@
       <c r="A43" t="s">
         <v>62</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3332,7 +3329,7 @@
       <c r="A45" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3761,12 +3758,12 @@
       </c>
     </row>
     <row r="120" ht="15.6" spans="1:1">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="121" ht="15.6" spans="1:1">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="5" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3789,7 +3786,7 @@
       <c r="A125" t="s">
         <v>143</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4088,11 +4085,11 @@
         <v>196</v>
       </c>
     </row>
-    <row r="209" ht="100.8" spans="1:3">
+    <row r="209" ht="28.8" spans="1:3">
       <c r="A209" t="s">
         <v>197</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="C209" s="8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4173,7 +4170,7 @@
       <c r="A237" t="s">
         <v>211</v>
       </c>
-      <c r="C237" s="9" t="s">
+      <c r="C237" s="8" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4215,7 +4212,7 @@
       <c r="A245" t="s">
         <v>220</v>
       </c>
-      <c r="C245" s="9" t="s">
+      <c r="C245" s="8" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4226,7 +4223,7 @@
       <c r="B246" t="s">
         <v>16</v>
       </c>
-      <c r="C246" s="9" t="s">
+      <c r="C246" s="8" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4342,7 +4339,7 @@
       </c>
     </row>
     <row r="288" ht="19.2" spans="1:1">
-      <c r="A288" s="10" t="s">
+      <c r="A288" s="9" t="s">
         <v>244</v>
       </c>
     </row>
@@ -4370,7 +4367,7 @@
       <c r="A297" t="s">
         <v>247</v>
       </c>
-      <c r="C297" s="9" t="s">
+      <c r="C297" s="8" t="s">
         <v>248</v>
       </c>
     </row>
@@ -4378,7 +4375,7 @@
       <c r="A298" t="s">
         <v>249</v>
       </c>
-      <c r="C298" s="9" t="s">
+      <c r="C298" s="8" t="s">
         <v>250</v>
       </c>
     </row>
